--- a/Docs/BossDesign.xlsx
+++ b/Docs/BossDesign.xlsx
@@ -54,18 +54,16 @@
     <definedName name="pw_Tolerance">'PowerLevel'!$B$34</definedName>
     <definedName name="range_Power">'PowerLevel'!$A$39:$B$44</definedName>
     <definedName name="list_Brain">'Enums'!$A$2:$A$5</definedName>
-    <definedName name="list_Targeting">'Enums'!$B$2:$B$12</definedName>
+    <definedName name="list_Targeting">'Enums'!$B$2:$B$18</definedName>
     <definedName name="list_Loot">'Enums'!$C$2:$C$14</definedName>
     <definedName name="list_Role">'Enums'!$D$2:$D$5</definedName>
     <definedName name="list_Bool">'Enums'!$E$2:$E$3</definedName>
-    <definedName name="list_EnemyCard">'Enums'!$F$2:$F$49</definedName>
+    <definedName name="list_EnemyCard">'Enums'!$F$2:$F$56</definedName>
     <definedName name="pow_Bat">'Summoned'!$B$3</definedName>
     <definedName name="pow_Goblin">'Summoned'!$B$4</definedName>
     <definedName name="pow_HeavyBandit">'Summoned'!$B$5</definedName>
     <definedName name="pow_LightBandit">'Summoned'!$B$6</definedName>
     <definedName name="pow_Pebble">'Summoned'!$B$7</definedName>
-    <definedName name="pow_Skeleton">'Summoned'!$B$8</definedName>
-    <definedName name="pow_Slime">'Summoned'!$B$9</definedName>
     <definedName name="pow_BlackKnight">'BlackKnight'!$B$16</definedName>
     <definedName name="pow_EvilKing">'EvilKing'!$B$16</definedName>
     <definedName name="pow_EvilKnight">'EvilKnight'!$B$16</definedName>
@@ -74,14 +72,14 @@
     <definedName name="pow_EvilWizard3">'EvilWizard3'!$B$16</definedName>
     <definedName name="pow_Reaper">'Reaper'!$B$16</definedName>
     <definedName name="pow_ReinforcedGolem">'ReinforcedGolem'!$B$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Roster'!$A$1:$Q$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Roster'!$A$1:$T$9</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="321">
   <si>
     <t>READ-ONLY - mirrored from Docs\EnemySheets.xlsx on every export. Edit the weights THERE; anything typed here is discarded on the next sync.</t>
   </si>
@@ -356,114 +354,135 @@
     <t>Ranger</t>
   </si>
   <si>
+    <t>ClosestIgnoreTotem</t>
+  </si>
+  <si>
+    <t>EarlyGame</t>
+  </si>
+  <si>
+    <t>Backline</t>
+  </si>
+  <si>
+    <t>Bite</t>
+  </si>
+  <si>
+    <t>Summoner</t>
+  </si>
+  <si>
     <t>Furthest</t>
   </si>
   <si>
-    <t>EarlyGame</t>
-  </si>
-  <si>
-    <t>Backline</t>
-  </si>
-  <si>
-    <t>Bite</t>
-  </si>
-  <si>
-    <t>Summoner</t>
+    <t>EarlyLevelReward</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>BlackGuard</t>
   </si>
   <si>
     <t>Random</t>
   </si>
   <si>
-    <t>EarlyLevelReward</t>
-  </si>
-  <si>
-    <t>Both</t>
-  </si>
-  <si>
-    <t>BlackGuard</t>
+    <t>EvilKingDrop</t>
+  </si>
+  <si>
+    <t>BoneBulwark</t>
   </si>
   <si>
     <t>RangerTargeting</t>
   </si>
   <si>
-    <t>EvilKingDrop</t>
-  </si>
-  <si>
-    <t>BoneBulwark</t>
+    <t>EvilKnightDrop</t>
+  </si>
+  <si>
+    <t>BoneChill</t>
   </si>
   <si>
     <t>Strongest</t>
   </si>
   <si>
-    <t>EvilKnightDrop</t>
-  </si>
-  <si>
-    <t>BoneChill</t>
+    <t>EvilWizard2Drop</t>
+  </si>
+  <si>
+    <t>BoulderSmash</t>
+  </si>
+  <si>
+    <t>StrongestIgnoreTotem</t>
+  </si>
+  <si>
+    <t>EvilWizard3Drop</t>
+  </si>
+  <si>
+    <t>CallReinforcements</t>
+  </si>
+  <si>
+    <t>Totem15Closest</t>
+  </si>
+  <si>
+    <t>EvilWizardDrop</t>
+  </si>
+  <si>
+    <t>CallTheDamned</t>
+  </si>
+  <si>
+    <t>Totem20Furthest</t>
+  </si>
+  <si>
+    <t>PoisonSkeleton</t>
+  </si>
+  <si>
+    <t>CallTheSwarm</t>
+  </si>
+  <si>
+    <t>Totem20Random</t>
+  </si>
+  <si>
+    <t>ReaperDrop</t>
+  </si>
+  <si>
+    <t>Chomp</t>
+  </si>
+  <si>
+    <t>Totem30Closest</t>
+  </si>
+  <si>
+    <t>ReinforcedGolemDrop</t>
+  </si>
+  <si>
+    <t>ClawAttack</t>
   </si>
   <si>
     <t>TotemClosest</t>
   </si>
   <si>
-    <t>EvilWizard2Drop</t>
-  </si>
-  <si>
-    <t>BoulderSmash</t>
+    <t>TutorialSapDrop</t>
+  </si>
+  <si>
+    <t>ConjureOoze</t>
   </si>
   <si>
     <t>TotemFurthest</t>
   </si>
   <si>
-    <t>EvilWizard3Drop</t>
-  </si>
-  <si>
-    <t>CallReinforcements</t>
+    <t>DarkBolt</t>
   </si>
   <si>
     <t>TotemWeakest</t>
   </si>
   <si>
-    <t>EvilWizardDrop</t>
-  </si>
-  <si>
-    <t>CallTheDamned</t>
+    <t>DeathsToll</t>
   </si>
   <si>
     <t>WarriorTargeting</t>
   </si>
   <si>
-    <t>PoisonSkeleton</t>
-  </si>
-  <si>
-    <t>CallTheSwarm</t>
+    <t>DreadCleave</t>
   </si>
   <si>
     <t>Weakest</t>
   </si>
   <si>
-    <t>ReaperDrop</t>
-  </si>
-  <si>
-    <t>Chomp</t>
-  </si>
-  <si>
-    <t>ReinforcedGolemDrop</t>
-  </si>
-  <si>
-    <t>ConjureOoze</t>
-  </si>
-  <si>
-    <t>TutorialSapDrop</t>
-  </si>
-  <si>
-    <t>DarkBolt</t>
-  </si>
-  <si>
-    <t>DeathsToll</t>
-  </si>
-  <si>
-    <t>DreadCleave</t>
-  </si>
-  <si>
     <t>EmberShroud</t>
   </si>
   <si>
@@ -482,6 +501,9 @@
     <t>Gnaw</t>
   </si>
   <si>
+    <t>GraveTithe</t>
+  </si>
+  <si>
     <t>HeavySwing</t>
   </si>
   <si>
@@ -494,12 +516,12 @@
     <t>MoveInnate</t>
   </si>
   <si>
+    <t>MoveInnate2</t>
+  </si>
+  <si>
     <t>Overflow</t>
   </si>
   <si>
-    <t>PincerGrip</t>
-  </si>
-  <si>
     <t>PlagueBite</t>
   </si>
   <si>
@@ -536,9 +558,15 @@
     <t>Slash+</t>
   </si>
   <si>
+    <t>SoulDrain</t>
+  </si>
+  <si>
     <t>SoulReap</t>
   </si>
   <si>
+    <t>SoulSwap</t>
+  </si>
+  <si>
     <t>SpikeBurst</t>
   </si>
   <si>
@@ -554,9 +582,18 @@
     <t>SummonImp</t>
   </si>
   <si>
+    <t>SummonPebble</t>
+  </si>
+  <si>
     <t>SummonSkeletonWarrior</t>
   </si>
   <si>
+    <t>TeleportInnate</t>
+  </si>
+  <si>
+    <t>VenomCut</t>
+  </si>
+  <si>
     <t>VoidBarrier</t>
   </si>
   <si>
@@ -602,255 +639,258 @@
     <t>ReinforcedGolem</t>
   </si>
   <si>
-    <t>Skeleton</t>
-  </si>
-  <si>
-    <t>BlackKnight, Reaper</t>
-  </si>
-  <si>
-    <t>Slime</t>
+    <t>Boss Name</t>
+  </si>
+  <si>
+    <t>BlackKnight</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>GUID</t>
+  </si>
+  <si>
+    <t>fae9e0d8df06f744cb3eed28f98bb54f</t>
+  </si>
+  <si>
+    <t>Sync</t>
+  </si>
+  <si>
+    <t>Stats (synced to Unity)</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>Black Knight</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>Actions Per Turn</t>
+  </si>
+  <si>
+    <t>Loot Table</t>
+  </si>
+  <si>
+    <t>Brandon's Power Level</t>
+  </si>
+  <si>
+    <t>Estimated Power Level</t>
+  </si>
+  <si>
+    <t>Delta (Estimated - Brandon's)</t>
+  </si>
+  <si>
+    <t>Average Card Power</t>
+  </si>
+  <si>
+    <t>Average Damage</t>
+  </si>
+  <si>
+    <t>Average Status Power</t>
+  </si>
+  <si>
+    <t>Average Summon Power</t>
+  </si>
+  <si>
+    <t>Deck</t>
+  </si>
+  <si>
+    <t>Actions from Card</t>
+  </si>
+  <si>
+    <t>8 damage</t>
+  </si>
+  <si>
+    <t>5 damage</t>
+  </si>
+  <si>
+    <t>Move 1</t>
+  </si>
+  <si>
+    <t>Counted</t>
+  </si>
+  <si>
+    <t>Card Facts</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Range Max</t>
+  </si>
+  <si>
+    <t>Tiles Hit</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>Poison Total</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>Shield</t>
+  </si>
+  <si>
+    <t>Block Total</t>
+  </si>
+  <si>
+    <t>Parry</t>
+  </si>
+  <si>
+    <t>Dodge</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>Weaken</t>
+  </si>
+  <si>
+    <t>Vulnerable</t>
+  </si>
+  <si>
+    <t>Frozen</t>
+  </si>
+  <si>
+    <t>Rooted</t>
+  </si>
+  <si>
+    <t>Taunt</t>
+  </si>
+  <si>
+    <t>Stealth</t>
+  </si>
+  <si>
+    <t>Poison Blade</t>
+  </si>
+  <si>
+    <t>Double Next Attack</t>
+  </si>
+  <si>
+    <t>Double Shield</t>
+  </si>
+  <si>
+    <t>Draw</t>
+  </si>
+  <si>
+    <t>Move Tiles</t>
+  </si>
+  <si>
+    <t>Summon Power</t>
+  </si>
+  <si>
+    <t>Cooldown</t>
+  </si>
+  <si>
+    <t>Card Power</t>
+  </si>
+  <si>
+    <t>Status Power</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>e58fd978e913eea4699c373a33b5e08b</t>
+  </si>
+  <si>
+    <t>Evil King</t>
+  </si>
+  <si>
+    <t>4 damage</t>
+  </si>
+  <si>
+    <t>3 damage</t>
+  </si>
+  <si>
+    <t>Summon</t>
+  </si>
+  <si>
+    <t>e6c2dbc2feb811c4dbfea4d90220a6a5</t>
+  </si>
+  <si>
+    <t>Evil Knight</t>
+  </si>
+  <si>
+    <t>6 damage, Parry x1</t>
+  </si>
+  <si>
+    <t>4 damage, Shield 10, Block x2</t>
+  </si>
+  <si>
+    <t>51a9fe976e746be4385a09a12bb4cc36</t>
+  </si>
+  <si>
+    <t>Evil Wizard</t>
+  </si>
+  <si>
+    <t>3 damage, Shield 7</t>
+  </si>
+  <si>
+    <t>Move 3</t>
+  </si>
+  <si>
+    <t>8a02da994bf78784c901145a07a767e4</t>
+  </si>
+  <si>
+    <t>Dread Sorcerer</t>
+  </si>
+  <si>
+    <t>6 damage</t>
+  </si>
+  <si>
+    <t>3 damage, Weaken 1, Vulnerable 1</t>
   </si>
   <si>
     <t>EvilWizard3</t>
   </si>
   <si>
-    <t>Boss Name</t>
-  </si>
-  <si>
-    <t>BlackKnight</t>
-  </si>
-  <si>
-    <t>Boss</t>
-  </si>
-  <si>
-    <t>GUID</t>
-  </si>
-  <si>
-    <t>fae9e0d8df06f744cb3eed28f98bb54f</t>
-  </si>
-  <si>
-    <t>Sync</t>
-  </si>
-  <si>
-    <t>Stats (synced to Unity)</t>
-  </si>
-  <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>Black Knight</t>
-  </si>
-  <si>
-    <t>Health</t>
-  </si>
-  <si>
-    <t>Actions Per Turn</t>
-  </si>
-  <si>
-    <t>Loot Table</t>
-  </si>
-  <si>
-    <t>Brandon's Power Level</t>
-  </si>
-  <si>
-    <t>Estimated Power Level</t>
-  </si>
-  <si>
-    <t>Delta (Estimated - Brandon's)</t>
-  </si>
-  <si>
-    <t>Average Card Power</t>
-  </si>
-  <si>
-    <t>Average Damage</t>
-  </si>
-  <si>
-    <t>Average Status Power</t>
-  </si>
-  <si>
-    <t>Average Summon Power</t>
-  </si>
-  <si>
-    <t>Deck</t>
-  </si>
-  <si>
-    <t>Actions from Card</t>
-  </si>
-  <si>
-    <t>8 damage</t>
-  </si>
-  <si>
-    <t>5 damage, Shield 10</t>
-  </si>
-  <si>
-    <t>Summon</t>
-  </si>
-  <si>
-    <t>Move 1</t>
-  </si>
-  <si>
-    <t>Counted</t>
-  </si>
-  <si>
-    <t>Card Facts</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Range Max</t>
-  </si>
-  <si>
-    <t>Tiles Hit</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>Poison Total</t>
-  </si>
-  <si>
-    <t>Heal</t>
-  </si>
-  <si>
-    <t>Shield</t>
-  </si>
-  <si>
-    <t>Block Total</t>
-  </si>
-  <si>
-    <t>Parry</t>
-  </si>
-  <si>
-    <t>Dodge</t>
-  </si>
-  <si>
-    <t>Strength</t>
-  </si>
-  <si>
-    <t>Weaken</t>
-  </si>
-  <si>
-    <t>Vulnerable</t>
-  </si>
-  <si>
-    <t>Frozen</t>
-  </si>
-  <si>
-    <t>Rooted</t>
-  </si>
-  <si>
-    <t>Taunt</t>
-  </si>
-  <si>
-    <t>Stealth</t>
-  </si>
-  <si>
-    <t>Poison Blade</t>
-  </si>
-  <si>
-    <t>Double Next Attack</t>
-  </si>
-  <si>
-    <t>Double Shield</t>
-  </si>
-  <si>
-    <t>Draw</t>
-  </si>
-  <si>
-    <t>Move Tiles</t>
-  </si>
-  <si>
-    <t>Summon Power</t>
-  </si>
-  <si>
-    <t>Cooldown</t>
-  </si>
-  <si>
-    <t>Card Power</t>
-  </si>
-  <si>
-    <t>Status Power</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>e58fd978e913eea4699c373a33b5e08b</t>
-  </si>
-  <si>
-    <t>Evil King</t>
-  </si>
-  <si>
-    <t>9 damage</t>
-  </si>
-  <si>
-    <t>e6c2dbc2feb811c4dbfea4d90220a6a5</t>
-  </si>
-  <si>
-    <t>Evil Knight</t>
-  </si>
-  <si>
-    <t>6 damage, Parry x1</t>
+    <t>e47742cc0b6bff34d80516b86f0ed93e</t>
+  </si>
+  <si>
+    <t>Emberlord</t>
+  </si>
+  <si>
+    <t>12 damage</t>
+  </si>
+  <si>
+    <t>Reaper</t>
+  </si>
+  <si>
+    <t>f5f2a9fce9bdff34a958576185c3c68b</t>
+  </si>
+  <si>
+    <t>2 damage, Weaken 1</t>
+  </si>
+  <si>
+    <t>4 damage, Vulnerable 1</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>2 damage</t>
+  </si>
+  <si>
+    <t>8d47800381e9665459f3b0826adf6b76</t>
+  </si>
+  <si>
+    <t>Reinforced Golem</t>
+  </si>
+  <si>
+    <t>7 damage</t>
   </si>
   <si>
     <t>4 damage, Shield 10</t>
   </si>
   <si>
-    <t>51a9fe976e746be4385a09a12bb4cc36</t>
-  </si>
-  <si>
-    <t>Evil Wizard</t>
-  </si>
-  <si>
-    <t>5 damage</t>
-  </si>
-  <si>
-    <t>3 damage, Shield 7</t>
-  </si>
-  <si>
-    <t>8a02da994bf78784c901145a07a767e4</t>
-  </si>
-  <si>
-    <t>Dread Sorcerer</t>
-  </si>
-  <si>
-    <t>6 damage</t>
-  </si>
-  <si>
-    <t>3 damage, Block x4</t>
-  </si>
-  <si>
-    <t>e47742cc0b6bff34d80516b86f0ed93e</t>
-  </si>
-  <si>
-    <t>Emberlord</t>
-  </si>
-  <si>
-    <t>4 damage, Shield 7</t>
-  </si>
-  <si>
-    <t>Reaper</t>
-  </si>
-  <si>
-    <t>f5f2a9fce9bdff34a958576185c3c68b</t>
-  </si>
-  <si>
-    <t>6 damage, Heal 5</t>
-  </si>
-  <si>
-    <t>4 damage, Vulnerable 1</t>
-  </si>
-  <si>
-    <t>8d47800381e9665459f3b0826adf6b76</t>
-  </si>
-  <si>
-    <t>Reinforced Golem</t>
-  </si>
-  <si>
-    <t>7 damage</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -917,7 +957,7 @@
     <t>Roster</t>
   </si>
   <si>
-    <t>Every body side by side, sorted by name, so you can see how they stack up. Fully formula-driven off the individual tabs.</t>
+    <t>Every body side by side, sorted by name - the bulk-edit grid. Display Name, Health, Actions Per Turn, Brain, Targeting, Loot Table, Role and Brandon's Power Level are plain values here, synced to the matching body tab exactly like the Inspector - edit either one. Renaming a body is done by typing its new name in the Name column. Boss, Deck Size and the averages stay read-only; Estimated/Effective Power/Delta/Flag recalculate from this row's own Health/Actions/Brandon's as you type, so they never go stale while you're still editing.</t>
   </si>
   <si>
     <t>Enums</t>
@@ -956,22 +996,22 @@
     <t>One button</t>
   </si>
   <si>
-    <t>In Unity: Tools &gt; Sync Bosses With Sheet. Applies your edits to Health, Actions Per Turn, Brain, Targeting, Loot Table, Role and Deck to the matching prefab, then refreshes this workbook so anything changed in the Inspector shows up here too.</t>
-  </si>
-  <si>
-    <t>One card name per column, left to right, no gaps - the first blank cell ends the deck. Duplicates are fine and expected (four Enemy Slash cards is four cells). Pick names from the dropdown so a typo cannot silently drop a card.</t>
-  </si>
-  <si>
-    <t>Brandon's Power Level and Notes</t>
-  </si>
-  <si>
-    <t>Never sync anywhere - they are authored HERE and preserved across every re-export.</t>
-  </si>
-  <si>
-    <t>Card Facts, Card Power, averages, Roster</t>
-  </si>
-  <si>
-    <t>Never hand-edit - fully derived from the prefab and its cards, rebuilt on every export.</t>
+    <t>In Unity: Tools &gt; Sync Bosses With Sheet. Applies your edits - typed on a body tab OR the Roster tab, whichever you used - to the matching prefab: Display Name, Health, Actions Per Turn, Brain, Targeting, Loot Table, Role, Brandon''s Power Level and Deck. Renaming a body''s Name on the Roster tab renames the prefab too, keeping its GUID (so decks and levels still point at it). Then refreshes this workbook so anything changed in the Inspector shows up here.</t>
+  </si>
+  <si>
+    <t>One card name per column, left to right, no gaps - the first blank cell ends the deck. Duplicates are fine and expected (four Enemy Slash cards is four cells). Pick names from the dropdown so a typo cannot silently drop a card. Only editable on the body tab - the Roster tab does not carry a Deck column.</t>
+  </si>
+  <si>
+    <t>Never syncs anywhere - authored HERE, body tab only, and preserved across every re-export.</t>
+  </si>
+  <si>
+    <t>Syncs between the body tab and the Roster tab - whichever one you typed in wins - but never reaches a prefab field directly. It only feeds Effective Power, which is what gets written to Character.powerLevel.</t>
+  </si>
+  <si>
+    <t>Card Facts, Card Power, averages</t>
+  </si>
+  <si>
+    <t>Never hand-edit - fully derived from the prefab and its cards, rebuilt on every export. On the Roster tab this is Avg Damage/Status/Summon/Card Power, Deck Size and Boss.</t>
   </si>
   <si>
     <t>Effective Power and Boss</t>
@@ -984,6 +1024,12 @@
   </si>
   <si>
     <t>That body is left alone on BOTH sides and named in the Unity console, the same conflict rule Docs/CardDesign.xlsx follows. Make them agree, or change only one, then sync again.</t>
+  </si>
+  <si>
+    <t>If the body tab and Roster disagree</t>
+  </si>
+  <si>
+    <t>Same idea, one layer earlier: whichever of the two changed since the last sync wins, but if BOTH changed - differently - since then, that body is left alone everywhere and named in the console. Make the two tabs agree, or change only one, then sync again.</t>
   </si>
   <si>
     <t>Regenerating without syncing</t>
@@ -1151,7 +1197,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>5</v>
@@ -2062,15 +2108,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>82</v>
@@ -2078,15 +2124,15 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B4" s="0">
         <f>IF($B$3="","NEW","Live")</f>
@@ -2094,20 +2140,20 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B8" s="0">
         <v>110</v>
@@ -2115,7 +2161,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
@@ -2126,7 +2172,7 @@
         <v>73</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -2139,7 +2185,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>119</v>
@@ -2155,7 +2201,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B15" s="0">
         <v>2</v>
@@ -2163,7 +2209,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B16" s="3">
         <f>IF($B$8="","",ROUND(($B$19*$B$9*pw_ActionScale+$B$8*pw_Health)/pw_Divisor,3))</f>
@@ -2171,7 +2217,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B17" s="3">
         <f>IF($B$15="","",ROUND($B$16-$B$15,3))</f>
@@ -2182,7 +2228,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$54:H$54),0)</f>
@@ -2190,7 +2236,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B20" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$32:H$32),0)</f>
@@ -2198,7 +2244,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B21" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$55:H$55),0)</f>
@@ -2206,7 +2252,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B22" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$52:H$52),0)</f>
@@ -2214,59 +2260,59 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>151</v>
+        <v>130</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B25" s="0" t="s">
+        <v>262</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>263</v>
+      </c>
+      <c r="D25" s="0" t="s">
+        <v>264</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="F25" s="0" t="s">
+        <v>265</v>
+      </c>
+      <c r="G25" s="0" t="s">
         <v>251</v>
       </c>
-      <c r="C25" s="0" t="s">
+      <c r="H25" s="0" t="s">
         <v>251</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>252</v>
-      </c>
-      <c r="F25" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="G25" s="0" t="s">
-        <v>201</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>82</v>
@@ -2275,10 +2321,10 @@
         <v>82</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>88</v>
@@ -2292,12 +2338,12 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B29" s="11">
         <v>1</v>
@@ -2312,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="11">
         <v>1</v>
@@ -2323,45 +2369,45 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B30" s="11">
         <v>2</v>
       </c>
       <c r="C30" s="11">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D30" s="11">
         <v>4</v>
       </c>
       <c r="E30" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B31" s="11">
         <v>1</v>
       </c>
       <c r="C31" s="11">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D31" s="11">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E31" s="11">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F31" s="11">
         <v>1</v>
@@ -2375,22 +2421,22 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B32" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C32" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D32" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -2427,7 +2473,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
@@ -2453,13 +2499,13 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B35" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C35" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D35" s="3">
         <v>0</v>
@@ -2479,7 +2525,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3">
         <v>0</v>
@@ -2505,7 +2551,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
         <v>0</v>
@@ -2531,7 +2577,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3">
         <v>0</v>
@@ -2557,7 +2603,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3">
         <v>0</v>
@@ -2583,7 +2629,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B40" s="3">
         <v>0</v>
@@ -2609,10 +2655,10 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41" s="3">
         <v>0</v>
@@ -2635,19 +2681,19 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B42" s="3">
         <v>0</v>
       </c>
       <c r="C42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -2661,7 +2707,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B43" s="3">
         <v>0</v>
@@ -2687,7 +2733,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -2713,7 +2759,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B45" s="3">
         <v>0</v>
@@ -2739,7 +2785,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3">
         <v>0</v>
@@ -2765,7 +2811,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3">
         <v>0</v>
@@ -2791,7 +2837,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B48" s="3">
         <v>0</v>
@@ -2817,7 +2863,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B49" s="3">
         <v>0</v>
@@ -2843,7 +2889,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -2869,7 +2915,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B51" s="3">
         <v>0</v>
@@ -2887,15 +2933,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B52" s="3">
         <v>0</v>
@@ -2910,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <f>pow_Skeleton</f>
+        <v>0</v>
       </c>
       <c r="G52" s="3">
         <v>0</v>
@@ -2921,7 +2967,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B53" s="11">
         <v>0</v>
@@ -2930,13 +2976,13 @@
         <v>0</v>
       </c>
       <c r="D53" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53" s="11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F53" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G53" s="11">
         <v>0</v>
@@ -2947,7 +2993,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B54" s="3">
         <f>B$32*pw_Damage+B$33+B$34*pw_Poison+B$35*pw_Heal+B$36*pw_Shield+B$37*pw_Block+B$38*pw_Parry+B$39*pw_Dodge+B$40*pw_Strength*pw_Horizon+B$41*pw_Weaken*pw_Horizon+B$42*pw_Vulnerable*pw_Horizon+B$43*pw_Frozen+B$44*pw_Rooted+B$45*pw_Taunt+B$46*pw_Stealth+B$47*pw_PoisonBlade*pw_Horizon+B$48*pw_DoubleNextAttack+B$49*pw_DoubleShield+B$50*pw_Draw+B$51*pw_Move+B$52*pw_Summon+MAX(0,B$31-1)*pw_Area</f>
@@ -2973,7 +3019,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3">
         <f>B$54-B$32*pw_Damage-B$33-B$52*pw_Summon</f>
@@ -2999,7 +3045,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B57" s="4"/>
     </row>
@@ -3060,15 +3106,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>82</v>
@@ -3076,15 +3122,15 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B4" s="0">
         <f>IF($B$3="","NEW","Live")</f>
@@ -3092,20 +3138,20 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B8" s="0">
         <v>150</v>
@@ -3113,7 +3159,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
@@ -3132,15 +3178,15 @@
         <v>74</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
@@ -3153,7 +3199,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B15" s="0">
         <v>2</v>
@@ -3161,7 +3207,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B16" s="3">
         <f>IF($B$8="","",ROUND(($B$19*$B$9*pw_ActionScale+$B$8*pw_Health)/pw_Divisor,3))</f>
@@ -3169,7 +3215,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B17" s="3">
         <f>IF($B$15="","",ROUND($B$16-$B$15,3))</f>
@@ -3180,7 +3226,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$54:H$54),0)</f>
@@ -3188,7 +3234,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B20" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$32:H$32),0)</f>
@@ -3196,7 +3242,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B21" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$55:H$55),0)</f>
@@ -3204,7 +3250,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B22" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$52:H$52),0)</f>
@@ -3212,59 +3258,59 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>237</v>
+        <v>269</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>82</v>
@@ -3290,12 +3336,12 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B29" s="11">
         <v>1</v>
@@ -3321,7 +3367,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B30" s="11">
         <v>1</v>
@@ -3347,7 +3393,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B31" s="11">
         <v>9</v>
@@ -3373,7 +3419,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B32" s="3">
         <v>7</v>
@@ -3425,7 +3471,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
@@ -3451,7 +3497,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B35" s="3">
         <v>0</v>
@@ -3477,7 +3523,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3">
         <v>0</v>
@@ -3503,7 +3549,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
         <v>0</v>
@@ -3529,7 +3575,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3">
         <v>0</v>
@@ -3555,7 +3601,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3">
         <v>0</v>
@@ -3581,7 +3627,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B40" s="3">
         <v>0</v>
@@ -3607,7 +3653,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B41" s="3">
         <v>0</v>
@@ -3633,7 +3679,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B42" s="3">
         <v>0</v>
@@ -3659,7 +3705,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B43" s="3">
         <v>0</v>
@@ -3685,7 +3731,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -3711,7 +3757,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B45" s="3">
         <v>0</v>
@@ -3737,7 +3783,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3">
         <v>0</v>
@@ -3763,7 +3809,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3">
         <v>0</v>
@@ -3789,7 +3835,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B48" s="3">
         <v>0</v>
@@ -3815,7 +3861,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B49" s="3">
         <v>0</v>
@@ -3841,7 +3887,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -3867,7 +3913,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B51" s="3">
         <v>0</v>
@@ -3893,7 +3939,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B52" s="3">
         <v>0</v>
@@ -3919,7 +3965,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B53" s="11">
         <v>0</v>
@@ -3945,7 +3991,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B54" s="3">
         <f>B$32*pw_Damage+B$33+B$34*pw_Poison+B$35*pw_Heal+B$36*pw_Shield+B$37*pw_Block+B$38*pw_Parry+B$39*pw_Dodge+B$40*pw_Strength*pw_Horizon+B$41*pw_Weaken*pw_Horizon+B$42*pw_Vulnerable*pw_Horizon+B$43*pw_Frozen+B$44*pw_Rooted+B$45*pw_Taunt+B$46*pw_Stealth+B$47*pw_PoisonBlade*pw_Horizon+B$48*pw_DoubleNextAttack+B$49*pw_DoubleShield+B$50*pw_Draw+B$51*pw_Move+B$52*pw_Summon+MAX(0,B$31-1)*pw_Area</f>
@@ -3971,7 +4017,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3">
         <f>B$54-B$32*pw_Damage-B$33-B$52*pw_Summon</f>
@@ -3997,7 +4043,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B57" s="4"/>
     </row>
@@ -4043,493 +4089,576 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="K1" s="1" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>267</v>
+        <v>278</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="B2" s="0" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="0">
-        <f>'BlackKnight'!B13</f>
-      </c>
-      <c r="D2" s="0">
-        <f>'BlackKnight'!B8</f>
+      <c r="D2" s="0" t="s">
+        <v>194</v>
       </c>
       <c r="E2" s="0">
-        <f>'BlackKnight'!B9</f>
+        <v>150</v>
       </c>
       <c r="F2" s="0">
-        <f>'BlackKnight'!B10</f>
-      </c>
-      <c r="G2" s="0">
-        <f>'BlackKnight'!B11</f>
-      </c>
-      <c r="H2" s="0">
+        <v>2</v>
+      </c>
+      <c r="G2" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="K2" s="0">
         <v>5</v>
       </c>
-      <c r="I2" s="3">
+      <c r="L2" s="3">
         <f>'BlackKnight'!B20</f>
       </c>
-      <c r="J2" s="3">
+      <c r="M2" s="3">
         <f>'BlackKnight'!B21</f>
       </c>
-      <c r="K2" s="3">
+      <c r="N2" s="3">
         <f>'BlackKnight'!B22</f>
       </c>
-      <c r="L2" s="3">
+      <c r="O2" s="3">
         <f>'BlackKnight'!B19</f>
       </c>
-      <c r="M2" s="3">
-        <f>'BlackKnight'!B16</f>
-      </c>
-      <c r="N2" s="3">
-        <f>'BlackKnight'!B15</f>
-      </c>
-      <c r="O2" s="3">
-        <f>IF(N2="",M2,N2)</f>
-      </c>
       <c r="P2" s="3">
-        <f>'BlackKnight'!B17</f>
-      </c>
-      <c r="Q2" s="0">
-        <f>IF(P2="","",IF(ABS(P2)&lt;=M2*pw_Tolerance,"OK",IF(P2&gt;0,"OVER","UNDER")))</f>
+        <f>IF(E2="","",ROUND((O2*F2*pw_ActionScale+E2*pw_Health)/pw_Divisor,3))</f>
+      </c>
+      <c r="Q2" s="3">
+        <v>2</v>
+      </c>
+      <c r="R2" s="3">
+        <f>IF(Q2="",P2,Q2)</f>
+      </c>
+      <c r="S2" s="3">
+        <f>IF(Q2="","",ROUND(P2-Q2,3))</f>
+      </c>
+      <c r="T2" s="0">
+        <f>IF(S2="","",IF(ABS(S2)&lt;=P2*pw_Tolerance,"OK",IF(S2&gt;0,"OVER","UNDER")))</f>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B3" s="0" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="0">
-        <f>'EvilKing'!B13</f>
-      </c>
-      <c r="D3" s="0">
-        <f>'EvilKing'!B8</f>
+      <c r="D3" s="0" t="s">
+        <v>240</v>
       </c>
       <c r="E3" s="0">
-        <f>'EvilKing'!B9</f>
+        <v>140</v>
       </c>
       <c r="F3" s="0">
-        <f>'EvilKing'!B10</f>
-      </c>
-      <c r="G3" s="0">
-        <f>'EvilKing'!B11</f>
-      </c>
-      <c r="H3" s="0">
+        <v>2</v>
+      </c>
+      <c r="G3" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="I3" s="0" t="s">
+        <v>101</v>
+      </c>
+      <c r="J3" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="K3" s="0">
         <v>7</v>
       </c>
-      <c r="I3" s="3">
+      <c r="L3" s="3">
         <f>'EvilKing'!B20</f>
       </c>
-      <c r="J3" s="3">
+      <c r="M3" s="3">
         <f>'EvilKing'!B21</f>
       </c>
-      <c r="K3" s="3">
+      <c r="N3" s="3">
         <f>'EvilKing'!B22</f>
       </c>
-      <c r="L3" s="3">
+      <c r="O3" s="3">
         <f>'EvilKing'!B19</f>
       </c>
-      <c r="M3" s="3">
-        <f>'EvilKing'!B16</f>
-      </c>
-      <c r="N3" s="3">
-        <f>'EvilKing'!B15</f>
-      </c>
-      <c r="O3" s="3">
-        <f>IF(N3="",M3,N3)</f>
-      </c>
       <c r="P3" s="3">
-        <f>'EvilKing'!B17</f>
-      </c>
-      <c r="Q3" s="0">
-        <f>IF(P3="","",IF(ABS(P3)&lt;=M3*pw_Tolerance,"OK",IF(P3&gt;0,"OVER","UNDER")))</f>
+        <f>IF(E3="","",ROUND((O3*F3*pw_ActionScale+E3*pw_Health)/pw_Divisor,3))</f>
+      </c>
+      <c r="Q3" s="3">
+        <v>2</v>
+      </c>
+      <c r="R3" s="3">
+        <f>IF(Q3="",P3,Q3)</f>
+      </c>
+      <c r="S3" s="3">
+        <f>IF(Q3="","",ROUND(P3-Q3,3))</f>
+      </c>
+      <c r="T3" s="0">
+        <f>IF(S3="","",IF(ABS(S3)&lt;=P3*pw_Tolerance,"OK",IF(S3&gt;0,"OVER","UNDER")))</f>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B4" s="0" t="s">
+        <v>244</v>
+      </c>
+      <c r="C4" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="0">
-        <f>'EvilKnight'!B13</f>
-      </c>
-      <c r="D4" s="0">
-        <f>'EvilKnight'!B8</f>
+      <c r="D4" s="0" t="s">
+        <v>245</v>
       </c>
       <c r="E4" s="0">
-        <f>'EvilKnight'!B9</f>
+        <v>130</v>
       </c>
       <c r="F4" s="0">
-        <f>'EvilKnight'!B10</f>
-      </c>
-      <c r="G4" s="0">
-        <f>'EvilKnight'!B11</f>
-      </c>
-      <c r="H4" s="0">
+        <v>2</v>
+      </c>
+      <c r="G4" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="0" t="s">
+        <v>104</v>
+      </c>
+      <c r="J4" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="K4" s="0">
         <v>7</v>
       </c>
-      <c r="I4" s="3">
+      <c r="L4" s="3">
         <f>'EvilKnight'!B20</f>
       </c>
-      <c r="J4" s="3">
+      <c r="M4" s="3">
         <f>'EvilKnight'!B21</f>
       </c>
-      <c r="K4" s="3">
+      <c r="N4" s="3">
         <f>'EvilKnight'!B22</f>
       </c>
-      <c r="L4" s="3">
+      <c r="O4" s="3">
         <f>'EvilKnight'!B19</f>
       </c>
-      <c r="M4" s="3">
-        <f>'EvilKnight'!B16</f>
-      </c>
-      <c r="N4" s="3">
-        <f>'EvilKnight'!B15</f>
-      </c>
-      <c r="O4" s="3">
-        <f>IF(N4="",M4,N4)</f>
-      </c>
       <c r="P4" s="3">
-        <f>'EvilKnight'!B17</f>
-      </c>
-      <c r="Q4" s="0">
-        <f>IF(P4="","",IF(ABS(P4)&lt;=M4*pw_Tolerance,"OK",IF(P4&gt;0,"OVER","UNDER")))</f>
+        <f>IF(E4="","",ROUND((O4*F4*pw_ActionScale+E4*pw_Health)/pw_Divisor,3))</f>
+      </c>
+      <c r="Q4" s="3">
+        <v>2</v>
+      </c>
+      <c r="R4" s="3">
+        <f>IF(Q4="",P4,Q4)</f>
+      </c>
+      <c r="S4" s="3">
+        <f>IF(Q4="","",ROUND(P4-Q4,3))</f>
+      </c>
+      <c r="T4" s="0">
+        <f>IF(S4="","",IF(ABS(S4)&lt;=P4*pw_Tolerance,"OK",IF(S4&gt;0,"OVER","UNDER")))</f>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B5" s="0" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="0">
-        <f>'EvilWizard'!B13</f>
-      </c>
-      <c r="D5" s="0">
-        <f>'EvilWizard'!B8</f>
+      <c r="D5" s="0" t="s">
+        <v>249</v>
       </c>
       <c r="E5" s="0">
-        <f>'EvilWizard'!B9</f>
+        <v>90</v>
       </c>
       <c r="F5" s="0">
-        <f>'EvilWizard'!B10</f>
-      </c>
-      <c r="G5" s="0">
-        <f>'EvilWizard'!B11</f>
-      </c>
-      <c r="H5" s="0">
+        <v>2</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="K5" s="0">
         <v>7</v>
       </c>
-      <c r="I5" s="3">
+      <c r="L5" s="3">
         <f>'EvilWizard'!B20</f>
       </c>
-      <c r="J5" s="3">
+      <c r="M5" s="3">
         <f>'EvilWizard'!B21</f>
       </c>
-      <c r="K5" s="3">
+      <c r="N5" s="3">
         <f>'EvilWizard'!B22</f>
       </c>
-      <c r="L5" s="3">
+      <c r="O5" s="3">
         <f>'EvilWizard'!B19</f>
       </c>
-      <c r="M5" s="3">
-        <f>'EvilWizard'!B16</f>
-      </c>
-      <c r="N5" s="3">
-        <f>'EvilWizard'!B15</f>
-      </c>
-      <c r="O5" s="3">
-        <f>IF(N5="",M5,N5)</f>
-      </c>
       <c r="P5" s="3">
-        <f>'EvilWizard'!B17</f>
-      </c>
-      <c r="Q5" s="0">
-        <f>IF(P5="","",IF(ABS(P5)&lt;=M5*pw_Tolerance,"OK",IF(P5&gt;0,"OVER","UNDER")))</f>
+        <f>IF(E5="","",ROUND((O5*F5*pw_ActionScale+E5*pw_Health)/pw_Divisor,3))</f>
+      </c>
+      <c r="Q5" s="3">
+        <v>2</v>
+      </c>
+      <c r="R5" s="3">
+        <f>IF(Q5="",P5,Q5)</f>
+      </c>
+      <c r="S5" s="3">
+        <f>IF(Q5="","",ROUND(P5-Q5,3))</f>
+      </c>
+      <c r="T5" s="0">
+        <f>IF(S5="","",IF(ABS(S5)&lt;=P5*pw_Tolerance,"OK",IF(S5&gt;0,"OVER","UNDER")))</f>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B6" s="0" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="0">
-        <f>'EvilWizard2'!B13</f>
-      </c>
-      <c r="D6" s="0">
-        <f>'EvilWizard2'!B8</f>
+      <c r="D6" s="0" t="s">
+        <v>253</v>
       </c>
       <c r="E6" s="0">
-        <f>'EvilWizard2'!B9</f>
+        <v>95</v>
       </c>
       <c r="F6" s="0">
-        <f>'EvilWizard2'!B10</f>
-      </c>
-      <c r="G6" s="0">
-        <f>'EvilWizard2'!B11</f>
-      </c>
-      <c r="H6" s="0">
+        <v>2</v>
+      </c>
+      <c r="G6" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="0" t="s">
+        <v>115</v>
+      </c>
+      <c r="I6" s="0" t="s">
+        <v>107</v>
+      </c>
+      <c r="J6" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="K6" s="0">
         <v>7</v>
       </c>
-      <c r="I6" s="3">
+      <c r="L6" s="3">
         <f>'EvilWizard2'!B20</f>
       </c>
-      <c r="J6" s="3">
+      <c r="M6" s="3">
         <f>'EvilWizard2'!B21</f>
       </c>
-      <c r="K6" s="3">
+      <c r="N6" s="3">
         <f>'EvilWizard2'!B22</f>
       </c>
-      <c r="L6" s="3">
+      <c r="O6" s="3">
         <f>'EvilWizard2'!B19</f>
       </c>
-      <c r="M6" s="3">
-        <f>'EvilWizard2'!B16</f>
-      </c>
-      <c r="N6" s="3">
-        <f>'EvilWizard2'!B15</f>
-      </c>
-      <c r="O6" s="3">
-        <f>IF(N6="",M6,N6)</f>
-      </c>
       <c r="P6" s="3">
-        <f>'EvilWizard2'!B17</f>
-      </c>
-      <c r="Q6" s="0">
-        <f>IF(P6="","",IF(ABS(P6)&lt;=M6*pw_Tolerance,"OK",IF(P6&gt;0,"OVER","UNDER")))</f>
+        <f>IF(E6="","",ROUND((O6*F6*pw_ActionScale+E6*pw_Health)/pw_Divisor,3))</f>
+      </c>
+      <c r="Q6" s="3">
+        <v>2</v>
+      </c>
+      <c r="R6" s="3">
+        <f>IF(Q6="",P6,Q6)</f>
+      </c>
+      <c r="S6" s="3">
+        <f>IF(Q6="","",ROUND(P6-Q6,3))</f>
+      </c>
+      <c r="T6" s="0">
+        <f>IF(S6="","",IF(ABS(S6)&lt;=P6*pw_Tolerance,"OK",IF(S6&gt;0,"OVER","UNDER")))</f>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>176</v>
+        <v>256</v>
       </c>
       <c r="B7" s="0" t="s">
+        <v>257</v>
+      </c>
+      <c r="C7" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="0">
-        <f>'EvilWizard3'!B13</f>
-      </c>
-      <c r="D7" s="0">
-        <f>'EvilWizard3'!B8</f>
+      <c r="D7" s="0" t="s">
+        <v>258</v>
       </c>
       <c r="E7" s="0">
-        <f>'EvilWizard3'!B9</f>
+        <v>60</v>
       </c>
       <c r="F7" s="0">
-        <f>'EvilWizard3'!B10</f>
-      </c>
-      <c r="G7" s="0">
-        <f>'EvilWizard3'!B11</f>
-      </c>
-      <c r="H7" s="0">
-        <v>7</v>
-      </c>
-      <c r="I7" s="3">
+        <v>2</v>
+      </c>
+      <c r="G7" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="0" t="s">
+        <v>106</v>
+      </c>
+      <c r="I7" s="0" t="s">
+        <v>110</v>
+      </c>
+      <c r="J7" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="K7" s="0">
+        <v>5</v>
+      </c>
+      <c r="L7" s="3">
         <f>'EvilWizard3'!B20</f>
       </c>
-      <c r="J7" s="3">
+      <c r="M7" s="3">
         <f>'EvilWizard3'!B21</f>
       </c>
-      <c r="K7" s="3">
+      <c r="N7" s="3">
         <f>'EvilWizard3'!B22</f>
       </c>
-      <c r="L7" s="3">
+      <c r="O7" s="3">
         <f>'EvilWizard3'!B19</f>
       </c>
-      <c r="M7" s="3">
-        <f>'EvilWizard3'!B16</f>
-      </c>
-      <c r="N7" s="3">
-        <f>'EvilWizard3'!B15</f>
-      </c>
-      <c r="O7" s="3">
-        <f>IF(N7="",M7,N7)</f>
-      </c>
       <c r="P7" s="3">
-        <f>'EvilWizard3'!B17</f>
-      </c>
-      <c r="Q7" s="0">
-        <f>IF(P7="","",IF(ABS(P7)&lt;=M7*pw_Tolerance,"OK",IF(P7&gt;0,"OVER","UNDER")))</f>
+        <f>IF(E7="","",ROUND((O7*F7*pw_ActionScale+E7*pw_Health)/pw_Divisor,3))</f>
+      </c>
+      <c r="Q7" s="3">
+        <v>2</v>
+      </c>
+      <c r="R7" s="3">
+        <f>IF(Q7="",P7,Q7)</f>
+      </c>
+      <c r="S7" s="3">
+        <f>IF(Q7="","",ROUND(P7-Q7,3))</f>
+      </c>
+      <c r="T7" s="0">
+        <f>IF(S7="","",IF(ABS(S7)&lt;=P7*pw_Tolerance,"OK",IF(S7&gt;0,"OVER","UNDER")))</f>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B8" s="0" t="s">
+        <v>261</v>
+      </c>
+      <c r="C8" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="C8" s="0">
-        <f>'Reaper'!B13</f>
-      </c>
-      <c r="D8" s="0">
-        <f>'Reaper'!B8</f>
+      <c r="D8" s="0" t="s">
+        <v>260</v>
       </c>
       <c r="E8" s="0">
-        <f>'Reaper'!B9</f>
+        <v>110</v>
       </c>
       <c r="F8" s="0">
-        <f>'Reaper'!B10</f>
-      </c>
-      <c r="G8" s="0">
-        <f>'Reaper'!B11</f>
-      </c>
-      <c r="H8" s="0">
+        <v>2</v>
+      </c>
+      <c r="G8" s="0" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="0" t="s">
+        <v>118</v>
+      </c>
+      <c r="I8" s="0" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="0">
         <v>7</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <f>'Reaper'!B20</f>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <f>'Reaper'!B21</f>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <f>'Reaper'!B22</f>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <f>'Reaper'!B19</f>
       </c>
-      <c r="M8" s="3">
-        <f>'Reaper'!B16</f>
-      </c>
-      <c r="N8" s="3">
-        <f>'Reaper'!B15</f>
-      </c>
-      <c r="O8" s="3">
-        <f>IF(N8="",M8,N8)</f>
-      </c>
       <c r="P8" s="3">
-        <f>'Reaper'!B17</f>
-      </c>
-      <c r="Q8" s="0">
-        <f>IF(P8="","",IF(ABS(P8)&lt;=M8*pw_Tolerance,"OK",IF(P8&gt;0,"OVER","UNDER")))</f>
+        <f>IF(E8="","",ROUND((O8*F8*pw_ActionScale+E8*pw_Health)/pw_Divisor,3))</f>
+      </c>
+      <c r="Q8" s="3">
+        <v>2</v>
+      </c>
+      <c r="R8" s="3">
+        <f>IF(Q8="",P8,Q8)</f>
+      </c>
+      <c r="S8" s="3">
+        <f>IF(Q8="","",ROUND(P8-Q8,3))</f>
+      </c>
+      <c r="T8" s="0">
+        <f>IF(S8="","",IF(ABS(S8)&lt;=P8*pw_Tolerance,"OK",IF(S8&gt;0,"OVER","UNDER")))</f>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B9" s="0" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" s="0" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="0">
-        <f>'ReinforcedGolem'!B13</f>
-      </c>
-      <c r="D9" s="0">
-        <f>'ReinforcedGolem'!B8</f>
+      <c r="D9" s="0" t="s">
+        <v>267</v>
       </c>
       <c r="E9" s="0">
-        <f>'ReinforcedGolem'!B9</f>
+        <v>150</v>
       </c>
       <c r="F9" s="0">
-        <f>'ReinforcedGolem'!B10</f>
-      </c>
-      <c r="G9" s="0">
-        <f>'ReinforcedGolem'!B11</f>
-      </c>
-      <c r="H9" s="0">
+        <v>2</v>
+      </c>
+      <c r="G9" s="0" t="s">
+        <v>95</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>122</v>
+      </c>
+      <c r="J9" s="0" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="0">
         <v>7</v>
       </c>
-      <c r="I9" s="3">
+      <c r="L9" s="3">
         <f>'ReinforcedGolem'!B20</f>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <f>'ReinforcedGolem'!B21</f>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <f>'ReinforcedGolem'!B22</f>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <f>'ReinforcedGolem'!B19</f>
       </c>
-      <c r="M9" s="3">
-        <f>'ReinforcedGolem'!B16</f>
-      </c>
-      <c r="N9" s="3">
-        <f>'ReinforcedGolem'!B15</f>
-      </c>
-      <c r="O9" s="3">
-        <f>IF(N9="",M9,N9)</f>
-      </c>
       <c r="P9" s="3">
-        <f>'ReinforcedGolem'!B17</f>
-      </c>
-      <c r="Q9" s="0">
-        <f>IF(P9="","",IF(ABS(P9)&lt;=M9*pw_Tolerance,"OK",IF(P9&gt;0,"OVER","UNDER")))</f>
+        <f>IF(E9="","",ROUND((O9*F9*pw_ActionScale+E9*pw_Health)/pw_Divisor,3))</f>
+      </c>
+      <c r="Q9" s="3">
+        <v>2</v>
+      </c>
+      <c r="R9" s="3">
+        <f>IF(Q9="",P9,Q9)</f>
+      </c>
+      <c r="S9" s="3">
+        <f>IF(Q9="","",ROUND(P9-Q9,3))</f>
+      </c>
+      <c r="T9" s="0">
+        <f>IF(S9="","",IF(ABS(S9)&lt;=P9*pw_Tolerance,"OK",IF(S9&gt;0,"OVER","UNDER")))</f>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q9"/>
-  <conditionalFormatting sqref="Q2:Q9">
+  <autoFilter ref="A1:T9"/>
+  <conditionalFormatting sqref="T2:T9">
     <cfRule priority="1" type="cellIs" operator="equal" dxfId="0">
       <formula>"OVER"</formula>
     </cfRule>
@@ -4540,13 +4669,27 @@
       <formula>"OK"</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" sqref="G2:G9" showErrorMessage="0" allowBlank="1">
+      <formula1>=list_Brain</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="H2:H9" showErrorMessage="0" allowBlank="1">
+      <formula1>=list_Targeting</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="I2:I9" showErrorMessage="0" allowBlank="1">
+      <formula1>=list_Loot</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="J2:J9" showErrorMessage="0" allowBlank="1">
+      <formula1>=list_Role</formula1>
+    </dataValidation>
+  </dataValidations>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4555,7 +4698,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="12" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
     </row>
     <row r="2">
@@ -4565,7 +4708,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4">
@@ -4575,55 +4718,55 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12">
@@ -4633,23 +4776,23 @@
     </row>
     <row r="13">
       <c r="A13" s="13" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
     </row>
     <row r="16">
@@ -4657,23 +4800,23 @@
         <v>76</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19">
@@ -4683,71 +4826,87 @@
     </row>
     <row r="20">
       <c r="A20" s="13" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>293</v>
+        <v>238</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>295</v>
+        <v>198</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>304</v>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -4757,7 +4916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -4943,194 +5102,247 @@
       </c>
     </row>
     <row r="13">
+      <c r="B13" s="0" t="s">
+        <v>121</v>
+      </c>
       <c r="C13" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
+      <c r="B14" s="0" t="s">
+        <v>124</v>
+      </c>
       <c r="C14" s="0" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15">
+      <c r="B15" s="0" t="s">
+        <v>127</v>
+      </c>
       <c r="F15" s="0" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16">
+      <c r="B16" s="0" t="s">
+        <v>129</v>
+      </c>
       <c r="F16" s="0" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17">
+      <c r="B17" s="0" t="s">
+        <v>131</v>
+      </c>
       <c r="F17" s="0" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
+      <c r="B18" s="0" t="s">
+        <v>133</v>
+      </c>
       <c r="F18" s="0" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
       <c r="F19" s="0" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20">
       <c r="F20" s="0" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21">
       <c r="F21" s="0" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22">
       <c r="F22" s="0" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23">
       <c r="F23" s="0" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24">
       <c r="F24" s="0" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25">
       <c r="F25" s="0" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26">
       <c r="F26" s="0" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27">
       <c r="F27" s="0" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28">
       <c r="F28" s="0" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29">
       <c r="F29" s="0" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30">
       <c r="F30" s="0" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31">
       <c r="F31" s="0" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32">
       <c r="F32" s="0" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33">
       <c r="F33" s="0" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34">
       <c r="F34" s="0" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35">
       <c r="F35" s="0" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36">
       <c r="F36" s="0" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37">
       <c r="F37" s="0" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38">
       <c r="F38" s="0" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39">
       <c r="F39" s="0" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40">
       <c r="F40" s="0" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41">
       <c r="F41" s="0" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42">
       <c r="F42" s="0" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43">
       <c r="F43" s="0" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44">
       <c r="F44" s="0" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45">
       <c r="F45" s="0" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46">
       <c r="F46" s="0" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47">
       <c r="F47" s="0" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48">
       <c r="F48" s="0" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49">
       <c r="F49" s="0" t="s">
-        <v>159</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="F50" s="0" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="F51" s="0" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="F52" s="0" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="F53" s="0" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="F54" s="0" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="F55" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="F56" s="0" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -5140,7 +5352,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -5150,95 +5362,73 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>71</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B3" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="B4" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="B5" s="10">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="B6" s="10">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="B7" s="10">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="10">
-        <v>2</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="10">
-        <v>2</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>
@@ -5261,15 +5451,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>82</v>
@@ -5277,15 +5467,15 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B4" s="0">
         <f>IF($B$3="","NEW","Live")</f>
@@ -5293,20 +5483,20 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B8" s="0">
         <v>150</v>
@@ -5314,7 +5504,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
@@ -5325,7 +5515,7 @@
         <v>73</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
@@ -5333,12 +5523,12 @@
         <v>74</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>86</v>
@@ -5354,7 +5544,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B15" s="0">
         <v>2</v>
@@ -5362,7 +5552,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B16" s="3">
         <f>IF($B$8="","",ROUND(($B$19*$B$9*pw_ActionScale+$B$8*pw_Health)/pw_Divisor,3))</f>
@@ -5370,7 +5560,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B17" s="3">
         <f>IF($B$15="","",ROUND($B$16-$B$15,3))</f>
@@ -5381,7 +5571,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3">
         <f>IFERROR(AVERAGEIF(B$26:F$26,"Yes",B$54:F$54),0)</f>
@@ -5389,7 +5579,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B20" s="3">
         <f>IFERROR(AVERAGEIF(B$26:F$26,"Yes",B$32:F$32),0)</f>
@@ -5397,7 +5587,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B21" s="3">
         <f>IFERROR(AVERAGEIF(B$26:F$26,"Yes",B$55:F$55),0)</f>
@@ -5405,7 +5595,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B22" s="3">
         <f>IFERROR(AVERAGEIF(B$26:F$26,"Yes",B$52:F$52),0)</f>
@@ -5413,47 +5603,47 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D24" s="0" t="s">
         <v>99</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>82</v>
@@ -5465,7 +5655,7 @@
         <v>82</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>88</v>
@@ -5473,12 +5663,12 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B29" s="11">
         <v>1</v>
@@ -5490,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="11">
         <v>1</v>
@@ -5498,7 +5688,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B30" s="11">
         <v>1</v>
@@ -5510,7 +5700,7 @@
         <v>1</v>
       </c>
       <c r="E30" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" s="11">
         <v>1</v>
@@ -5518,7 +5708,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B31" s="11">
         <v>9</v>
@@ -5538,7 +5728,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B32" s="3">
         <v>8</v>
@@ -5550,7 +5740,7 @@
         <v>5</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -5578,7 +5768,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
@@ -5598,7 +5788,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B35" s="3">
         <v>0</v>
@@ -5618,7 +5808,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3">
         <v>0</v>
@@ -5627,7 +5817,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3">
         <v>0</v>
@@ -5638,7 +5828,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
         <v>0</v>
@@ -5658,7 +5848,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3">
         <v>0</v>
@@ -5678,7 +5868,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3">
         <v>0</v>
@@ -5698,7 +5888,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B40" s="3">
         <v>0</v>
@@ -5718,7 +5908,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B41" s="3">
         <v>0</v>
@@ -5738,7 +5928,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B42" s="3">
         <v>0</v>
@@ -5758,7 +5948,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B43" s="3">
         <v>0</v>
@@ -5778,7 +5968,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -5798,7 +5988,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B45" s="3">
         <v>0</v>
@@ -5818,7 +6008,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3">
         <v>0</v>
@@ -5838,7 +6028,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3">
         <v>0</v>
@@ -5858,7 +6048,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B48" s="3">
         <v>0</v>
@@ -5878,7 +6068,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B49" s="3">
         <v>0</v>
@@ -5898,7 +6088,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -5918,7 +6108,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B51" s="3">
         <v>0</v>
@@ -5938,7 +6128,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B52" s="3">
         <v>0</v>
@@ -5950,7 +6140,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="3">
-        <f>pow_Skeleton</f>
+        <v>0</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
@@ -5958,7 +6148,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B53" s="11">
         <v>0</v>
@@ -5970,7 +6160,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F53" s="11">
         <v>0</v>
@@ -5978,7 +6168,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B54" s="3">
         <f>B$32*pw_Damage+B$33+B$34*pw_Poison+B$35*pw_Heal+B$36*pw_Shield+B$37*pw_Block+B$38*pw_Parry+B$39*pw_Dodge+B$40*pw_Strength*pw_Horizon+B$41*pw_Weaken*pw_Horizon+B$42*pw_Vulnerable*pw_Horizon+B$43*pw_Frozen+B$44*pw_Rooted+B$45*pw_Taunt+B$46*pw_Stealth+B$47*pw_PoisonBlade*pw_Horizon+B$48*pw_DoubleNextAttack+B$49*pw_DoubleShield+B$50*pw_Draw+B$51*pw_Move+B$52*pw_Summon+MAX(0,B$31-1)*pw_Area</f>
@@ -5998,7 +6188,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3">
         <f>B$54-B$32*pw_Damage-B$33-B$52*pw_Summon</f>
@@ -6018,7 +6208,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B57" s="4"/>
     </row>
@@ -6073,15 +6263,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>82</v>
@@ -6089,15 +6279,15 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B4" s="0">
         <f>IF($B$3="","NEW","Live")</f>
@@ -6105,20 +6295,20 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B8" s="0">
         <v>140</v>
@@ -6126,7 +6316,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
@@ -6137,7 +6327,7 @@
         <v>73</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -6145,12 +6335,12 @@
         <v>74</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>101</v>
@@ -6166,7 +6356,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B15" s="0">
         <v>2</v>
@@ -6174,7 +6364,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B16" s="3">
         <f>IF($B$8="","",ROUND(($B$19*$B$9*pw_ActionScale+$B$8*pw_Health)/pw_Divisor,3))</f>
@@ -6182,7 +6372,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B17" s="3">
         <f>IF($B$15="","",ROUND($B$16-$B$15,3))</f>
@@ -6193,7 +6383,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$54:H$54),0)</f>
@@ -6201,7 +6391,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B20" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$32:H$32),0)</f>
@@ -6209,7 +6399,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B21" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$55:H$55),0)</f>
@@ -6217,7 +6407,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B22" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$52:H$52),0)</f>
@@ -6225,59 +6415,59 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>82</v>
@@ -6303,12 +6493,12 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B29" s="11">
         <v>1</v>
@@ -6334,7 +6524,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B30" s="11">
         <v>1</v>
@@ -6360,7 +6550,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B31" s="11">
         <v>1</v>
@@ -6386,19 +6576,19 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B32" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C32" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D32" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -6438,7 +6628,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
@@ -6464,7 +6654,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B35" s="3">
         <v>0</v>
@@ -6490,7 +6680,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3">
         <v>0</v>
@@ -6499,10 +6689,10 @@
         <v>0</v>
       </c>
       <c r="D36" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F36" s="3">
         <v>0</v>
@@ -6516,7 +6706,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
         <v>0</v>
@@ -6542,7 +6732,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3">
         <v>0</v>
@@ -6568,7 +6758,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3">
         <v>0</v>
@@ -6594,7 +6784,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B40" s="3">
         <v>0</v>
@@ -6620,7 +6810,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B41" s="3">
         <v>0</v>
@@ -6646,7 +6836,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B42" s="3">
         <v>0</v>
@@ -6672,7 +6862,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B43" s="3">
         <v>0</v>
@@ -6698,7 +6888,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -6724,7 +6914,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B45" s="3">
         <v>0</v>
@@ -6750,7 +6940,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3">
         <v>0</v>
@@ -6776,7 +6966,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3">
         <v>0</v>
@@ -6802,7 +6992,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B48" s="3">
         <v>0</v>
@@ -6828,7 +7018,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B49" s="3">
         <v>0</v>
@@ -6854,7 +7044,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -6880,7 +7070,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B51" s="3">
         <v>0</v>
@@ -6906,7 +7096,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B52" s="3">
         <v>0</v>
@@ -6932,7 +7122,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B53" s="11">
         <v>0</v>
@@ -6958,7 +7148,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B54" s="3">
         <f>B$32*pw_Damage+B$33+B$34*pw_Poison+B$35*pw_Heal+B$36*pw_Shield+B$37*pw_Block+B$38*pw_Parry+B$39*pw_Dodge+B$40*pw_Strength*pw_Horizon+B$41*pw_Weaken*pw_Horizon+B$42*pw_Vulnerable*pw_Horizon+B$43*pw_Frozen+B$44*pw_Rooted+B$45*pw_Taunt+B$46*pw_Stealth+B$47*pw_PoisonBlade*pw_Horizon+B$48*pw_DoubleNextAttack+B$49*pw_DoubleShield+B$50*pw_Draw+B$51*pw_Move+B$52*pw_Summon+MAX(0,B$31-1)*pw_Area</f>
@@ -6984,7 +7174,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3">
         <f>B$54-B$32*pw_Damage-B$33-B$52*pw_Summon</f>
@@ -7010,7 +7200,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B57" s="4"/>
     </row>
@@ -7071,15 +7261,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>82</v>
@@ -7087,15 +7277,15 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B4" s="0">
         <f>IF($B$3="","NEW","Live")</f>
@@ -7103,20 +7293,20 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B8" s="0">
         <v>130</v>
@@ -7124,7 +7314,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
@@ -7148,7 +7338,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>104</v>
@@ -7164,7 +7354,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B15" s="0">
         <v>2</v>
@@ -7172,7 +7362,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B16" s="3">
         <f>IF($B$8="","",ROUND(($B$19*$B$9*pw_ActionScale+$B$8*pw_Health)/pw_Divisor,3))</f>
@@ -7180,7 +7370,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B17" s="3">
         <f>IF($B$15="","",ROUND($B$16-$B$15,3))</f>
@@ -7191,7 +7381,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$54:H$54),0)</f>
@@ -7199,7 +7389,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B20" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$32:H$32),0)</f>
@@ -7207,7 +7397,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B21" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$55:H$55),0)</f>
@@ -7215,7 +7405,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B22" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$52:H$52),0)</f>
@@ -7223,59 +7413,59 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>82</v>
@@ -7301,12 +7491,12 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B29" s="11">
         <v>1</v>
@@ -7332,7 +7522,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B30" s="11">
         <v>1</v>
@@ -7358,7 +7548,7 @@
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B31" s="11">
         <v>1</v>
@@ -7373,7 +7563,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="11">
         <v>1</v>
@@ -7384,7 +7574,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B32" s="3">
         <v>6</v>
@@ -7436,7 +7626,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
@@ -7462,7 +7652,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B35" s="3">
         <v>0</v>
@@ -7488,7 +7678,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3">
         <v>0</v>
@@ -7514,7 +7704,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
         <v>0</v>
@@ -7523,10 +7713,10 @@
         <v>0</v>
       </c>
       <c r="D37" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E37" s="3">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F37" s="3">
         <v>0</v>
@@ -7540,7 +7730,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3">
         <v>1</v>
@@ -7566,7 +7756,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3">
         <v>0</v>
@@ -7592,7 +7782,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B40" s="3">
         <v>0</v>
@@ -7618,7 +7808,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B41" s="3">
         <v>0</v>
@@ -7644,7 +7834,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B42" s="3">
         <v>0</v>
@@ -7670,7 +7860,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B43" s="3">
         <v>0</v>
@@ -7696,7 +7886,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -7722,7 +7912,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B45" s="3">
         <v>0</v>
@@ -7748,7 +7938,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3">
         <v>0</v>
@@ -7774,7 +7964,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3">
         <v>0</v>
@@ -7800,7 +7990,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B48" s="3">
         <v>0</v>
@@ -7826,7 +8016,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B49" s="3">
         <v>0</v>
@@ -7852,7 +8042,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -7878,7 +8068,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B51" s="3">
         <v>0</v>
@@ -7904,7 +8094,7 @@
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B52" s="3">
         <v>0</v>
@@ -7930,7 +8120,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B53" s="11">
         <v>0</v>
@@ -7956,7 +8146,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B54" s="3">
         <f>B$32*pw_Damage+B$33+B$34*pw_Poison+B$35*pw_Heal+B$36*pw_Shield+B$37*pw_Block+B$38*pw_Parry+B$39*pw_Dodge+B$40*pw_Strength*pw_Horizon+B$41*pw_Weaken*pw_Horizon+B$42*pw_Vulnerable*pw_Horizon+B$43*pw_Frozen+B$44*pw_Rooted+B$45*pw_Taunt+B$46*pw_Stealth+B$47*pw_PoisonBlade*pw_Horizon+B$48*pw_DoubleNextAttack+B$49*pw_DoubleShield+B$50*pw_Draw+B$51*pw_Move+B$52*pw_Summon+MAX(0,B$31-1)*pw_Area</f>
@@ -7982,7 +8172,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3">
         <f>B$54-B$32*pw_Damage-B$33-B$52*pw_Summon</f>
@@ -8008,7 +8198,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B57" s="4"/>
     </row>
@@ -8069,15 +8259,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>82</v>
@@ -8085,15 +8275,15 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B4" s="0">
         <f>IF($B$3="","NEW","Live")</f>
@@ -8101,20 +8291,20 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B8" s="0">
         <v>90</v>
@@ -8122,7 +8312,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
@@ -8141,12 +8331,12 @@
         <v>74</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>113</v>
@@ -8162,7 +8352,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B15" s="0">
         <v>2</v>
@@ -8170,7 +8360,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B16" s="3">
         <f>IF($B$8="","",ROUND(($B$19*$B$9*pw_ActionScale+$B$8*pw_Health)/pw_Divisor,3))</f>
@@ -8178,7 +8368,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B17" s="3">
         <f>IF($B$15="","",ROUND($B$16-$B$15,3))</f>
@@ -8189,7 +8379,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$54:H$54),0)</f>
@@ -8197,7 +8387,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B20" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$32:H$32),0)</f>
@@ -8205,7 +8395,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B21" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$55:H$55),0)</f>
@@ -8213,7 +8403,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B22" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$52:H$52),0)</f>
@@ -8221,59 +8411,59 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>82</v>
@@ -8299,12 +8489,12 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B29" s="11">
         <v>1</v>
@@ -8330,7 +8520,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B30" s="11">
         <v>5</v>
@@ -8348,21 +8538,21 @@
         <v>3</v>
       </c>
       <c r="G30" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B31" s="11">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C31" s="11">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D31" s="11">
         <v>1</v>
@@ -8382,7 +8572,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B32" s="3">
         <v>5</v>
@@ -8434,7 +8624,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
@@ -8460,7 +8650,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B35" s="3">
         <v>0</v>
@@ -8486,7 +8676,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3">
         <v>0</v>
@@ -8512,7 +8702,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
         <v>0</v>
@@ -8538,7 +8728,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3">
         <v>0</v>
@@ -8564,7 +8754,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3">
         <v>0</v>
@@ -8590,7 +8780,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B40" s="3">
         <v>0</v>
@@ -8616,7 +8806,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B41" s="3">
         <v>0</v>
@@ -8642,7 +8832,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B42" s="3">
         <v>0</v>
@@ -8668,7 +8858,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B43" s="3">
         <v>0</v>
@@ -8694,7 +8884,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -8720,7 +8910,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B45" s="3">
         <v>0</v>
@@ -8746,7 +8936,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3">
         <v>0</v>
@@ -8772,7 +8962,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3">
         <v>0</v>
@@ -8798,7 +8988,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B48" s="3">
         <v>0</v>
@@ -8824,7 +9014,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B49" s="3">
         <v>0</v>
@@ -8850,7 +9040,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -8876,7 +9066,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B51" s="3">
         <v>0</v>
@@ -8894,15 +9084,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B52" s="3">
         <v>0</v>
@@ -8928,7 +9118,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B53" s="11">
         <v>0</v>
@@ -8954,7 +9144,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B54" s="3">
         <f>B$32*pw_Damage+B$33+B$34*pw_Poison+B$35*pw_Heal+B$36*pw_Shield+B$37*pw_Block+B$38*pw_Parry+B$39*pw_Dodge+B$40*pw_Strength*pw_Horizon+B$41*pw_Weaken*pw_Horizon+B$42*pw_Vulnerable*pw_Horizon+B$43*pw_Frozen+B$44*pw_Rooted+B$45*pw_Taunt+B$46*pw_Stealth+B$47*pw_PoisonBlade*pw_Horizon+B$48*pw_DoubleNextAttack+B$49*pw_DoubleShield+B$50*pw_Draw+B$51*pw_Move+B$52*pw_Summon+MAX(0,B$31-1)*pw_Area</f>
@@ -8980,7 +9170,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3">
         <f>B$54-B$32*pw_Damage-B$33-B$52*pw_Summon</f>
@@ -9006,7 +9196,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B57" s="4"/>
     </row>
@@ -9067,15 +9257,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="0" t="s">
         <v>177</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>82</v>
@@ -9083,15 +9273,15 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B4" s="0">
         <f>IF($B$3="","NEW","Live")</f>
@@ -9099,20 +9289,20 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B8" s="0">
         <v>95</v>
@@ -9120,7 +9310,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
@@ -9139,12 +9329,12 @@
         <v>74</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>107</v>
@@ -9160,7 +9350,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B15" s="0">
         <v>2</v>
@@ -9168,7 +9358,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B16" s="3">
         <f>IF($B$8="","",ROUND(($B$19*$B$9*pw_ActionScale+$B$8*pw_Health)/pw_Divisor,3))</f>
@@ -9176,7 +9366,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B17" s="3">
         <f>IF($B$15="","",ROUND($B$16-$B$15,3))</f>
@@ -9187,7 +9377,7 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$54:H$54),0)</f>
@@ -9195,7 +9385,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B20" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$32:H$32),0)</f>
@@ -9203,7 +9393,7 @@
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B21" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$55:H$55),0)</f>
@@ -9211,7 +9401,7 @@
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B22" s="3">
         <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$52:H$52),0)</f>
@@ -9219,7 +9409,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B24" s="0" t="s">
         <v>83</v>
@@ -9228,50 +9418,50 @@
         <v>83</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="F24" s="0" t="s">
         <v>117</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="H24" s="0" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>200</v>
+        <v>243</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>82</v>
@@ -9297,12 +9487,12 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B29" s="11">
         <v>1</v>
@@ -9328,7 +9518,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B30" s="11">
         <v>5</v>
@@ -9346,15 +9536,15 @@
         <v>3</v>
       </c>
       <c r="G30" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H30" s="11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B31" s="11">
         <v>1</v>
@@ -9380,7 +9570,7 @@
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B32" s="3">
         <v>6</v>
@@ -9432,7 +9622,7 @@
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
@@ -9458,7 +9648,7 @@
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B35" s="3">
         <v>0</v>
@@ -9484,7 +9674,7 @@
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3">
         <v>0</v>
@@ -9510,7 +9700,7 @@
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
         <v>0</v>
@@ -9519,10 +9709,10 @@
         <v>0</v>
       </c>
       <c r="D37" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E37" s="3">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F37" s="3">
         <v>0</v>
@@ -9536,7 +9726,7 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3">
         <v>0</v>
@@ -9562,7 +9752,7 @@
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3">
         <v>0</v>
@@ -9588,7 +9778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B40" s="3">
         <v>0</v>
@@ -9614,7 +9804,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B41" s="3">
         <v>0</v>
@@ -9623,10 +9813,10 @@
         <v>0</v>
       </c>
       <c r="D41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="3">
         <v>0</v>
@@ -9640,7 +9830,7 @@
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B42" s="3">
         <v>0</v>
@@ -9649,10 +9839,10 @@
         <v>0</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -9666,7 +9856,7 @@
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B43" s="3">
         <v>0</v>
@@ -9692,7 +9882,7 @@
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -9718,7 +9908,7 @@
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B45" s="3">
         <v>0</v>
@@ -9744,7 +9934,7 @@
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3">
         <v>0</v>
@@ -9770,7 +9960,7 @@
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3">
         <v>0</v>
@@ -9796,7 +9986,7 @@
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B48" s="3">
         <v>0</v>
@@ -9822,7 +10012,7 @@
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B49" s="3">
         <v>0</v>
@@ -9848,7 +10038,7 @@
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -9874,7 +10064,7 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B51" s="3">
         <v>0</v>
@@ -9892,15 +10082,15 @@
         <v>0</v>
       </c>
       <c r="G51" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B52" s="3">
         <v>0</v>
@@ -9926,7 +10116,7 @@
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B53" s="11">
         <v>0</v>
@@ -9952,7 +10142,7 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B54" s="3">
         <f>B$32*pw_Damage+B$33+B$34*pw_Poison+B$35*pw_Heal+B$36*pw_Shield+B$37*pw_Block+B$38*pw_Parry+B$39*pw_Dodge+B$40*pw_Strength*pw_Horizon+B$41*pw_Weaken*pw_Horizon+B$42*pw_Vulnerable*pw_Horizon+B$43*pw_Frozen+B$44*pw_Rooted+B$45*pw_Taunt+B$46*pw_Stealth+B$47*pw_PoisonBlade*pw_Horizon+B$48*pw_DoubleNextAttack+B$49*pw_DoubleShield+B$50*pw_Draw+B$51*pw_Move+B$52*pw_Summon+MAX(0,B$31-1)*pw_Area</f>
@@ -9978,7 +10168,7 @@
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3">
         <f>B$54-B$32*pw_Damage-B$33-B$52*pw_Summon</f>
@@ -10004,7 +10194,7 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B57" s="4"/>
     </row>
@@ -10050,7 +10240,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H57"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -10059,21 +10249,19 @@
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>176</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>82</v>
@@ -10081,15 +10269,15 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="B4" s="0">
         <f>IF($B$3="","NEW","Live")</f>
@@ -10097,28 +10285,28 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="B8" s="0">
-        <v>100</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="B9" s="0">
         <v>2</v>
@@ -10129,7 +10317,7 @@
         <v>73</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -10137,12 +10325,12 @@
         <v>74</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="B12" s="0" t="s">
         <v>110</v>
@@ -10158,7 +10346,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B15" s="0">
         <v>2</v>
@@ -10166,7 +10354,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B16" s="3">
         <f>IF($B$8="","",ROUND(($B$19*$B$9*pw_ActionScale+$B$8*pw_Health)/pw_Divisor,3))</f>
@@ -10174,7 +10362,7 @@
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="B17" s="3">
         <f>IF($B$15="","",ROUND($B$16-$B$15,3))</f>
@@ -10185,91 +10373,79 @@
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="B19" s="3">
-        <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$54:H$54),0)</f>
+        <f>IFERROR(AVERAGEIF(B$26:F$26,"Yes",B$54:F$54),0)</f>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="B20" s="3">
-        <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$32:H$32),0)</f>
+        <f>IFERROR(AVERAGEIF(B$26:F$26,"Yes",B$32:F$32),0)</f>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="B21" s="3">
-        <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$55:H$55),0)</f>
+        <f>IFERROR(AVERAGEIF(B$26:F$26,"Yes",B$55:F$55),0)</f>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="B22" s="3">
-        <f>IFERROR(AVERAGEIF(B$26:H$26,"Yes",B$52:H$52),0)</f>
+        <f>IFERROR(AVERAGEIF(B$26:F$26,"Yes",B$52:F$52),0)</f>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>122</v>
-      </c>
-      <c r="G24" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="H24" s="0" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>200</v>
-      </c>
-      <c r="G25" s="0" t="s">
-        <v>201</v>
-      </c>
-      <c r="H25" s="0" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="B26" s="0" t="s">
         <v>82</v>
@@ -10281,26 +10457,20 @@
         <v>82</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F26" s="0" t="s">
         <v>88</v>
       </c>
-      <c r="G26" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="H26" s="0" t="s">
-        <v>88</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B29" s="11">
         <v>1</v>
@@ -10315,18 +10485,12 @@
         <v>1</v>
       </c>
       <c r="F29" s="11">
-        <v>0</v>
-      </c>
-      <c r="G29" s="11">
-        <v>1</v>
-      </c>
-      <c r="H29" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="B30" s="11">
         <v>5</v>
@@ -10335,30 +10499,24 @@
         <v>5</v>
       </c>
       <c r="D30" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E30" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F30" s="11">
         <v>3</v>
       </c>
-      <c r="G30" s="11">
-        <v>1</v>
-      </c>
-      <c r="H30" s="11">
-        <v>1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B31" s="11">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C31" s="11">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D31" s="11">
         <v>1</v>
@@ -10367,38 +10525,26 @@
         <v>1</v>
       </c>
       <c r="F31" s="11">
-        <v>1</v>
-      </c>
-      <c r="G31" s="11">
-        <v>1</v>
-      </c>
-      <c r="H31" s="11">
         <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B32" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C32" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D32" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E32" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
         <v>0</v>
       </c>
     </row>
@@ -10421,16 +10567,10 @@
       <c r="F33" s="3">
         <f>IFERROR(VLOOKUP(F$30,range_Power,2,TRUE),0)</f>
       </c>
-      <c r="G33" s="3">
-        <f>IFERROR(VLOOKUP(G$30,range_Power,2,TRUE),0)</f>
-      </c>
-      <c r="H33" s="3">
-        <f>IFERROR(VLOOKUP(H$30,range_Power,2,TRUE),0)</f>
-      </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="B34" s="3">
         <v>0</v>
@@ -10445,18 +10585,12 @@
         <v>0</v>
       </c>
       <c r="F34" s="3">
-        <v>0</v>
-      </c>
-      <c r="G34" s="3">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B35" s="3">
         <v>0</v>
@@ -10471,18 +10605,12 @@
         <v>0</v>
       </c>
       <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B36" s="3">
         <v>0</v>
@@ -10491,24 +10619,18 @@
         <v>0</v>
       </c>
       <c r="D36" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E36" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F36" s="3">
-        <v>0</v>
-      </c>
-      <c r="G36" s="3">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B37" s="3">
         <v>0</v>
@@ -10523,18 +10645,12 @@
         <v>0</v>
       </c>
       <c r="F37" s="3">
-        <v>0</v>
-      </c>
-      <c r="G37" s="3">
-        <v>0</v>
-      </c>
-      <c r="H37" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="B38" s="3">
         <v>0</v>
@@ -10549,18 +10665,12 @@
         <v>0</v>
       </c>
       <c r="F38" s="3">
-        <v>0</v>
-      </c>
-      <c r="G38" s="3">
-        <v>0</v>
-      </c>
-      <c r="H38" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B39" s="3">
         <v>0</v>
@@ -10575,18 +10685,12 @@
         <v>0</v>
       </c>
       <c r="F39" s="3">
-        <v>0</v>
-      </c>
-      <c r="G39" s="3">
-        <v>0</v>
-      </c>
-      <c r="H39" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="B40" s="3">
         <v>0</v>
@@ -10601,18 +10705,12 @@
         <v>0</v>
       </c>
       <c r="F40" s="3">
-        <v>0</v>
-      </c>
-      <c r="G40" s="3">
-        <v>0</v>
-      </c>
-      <c r="H40" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B41" s="3">
         <v>0</v>
@@ -10627,18 +10725,12 @@
         <v>0</v>
       </c>
       <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B42" s="3">
         <v>0</v>
@@ -10653,18 +10745,12 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B43" s="3">
         <v>0</v>
@@ -10679,18 +10765,12 @@
         <v>0</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B44" s="3">
         <v>0</v>
@@ -10705,18 +10785,12 @@
         <v>0</v>
       </c>
       <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B45" s="3">
         <v>0</v>
@@ -10731,18 +10805,12 @@
         <v>0</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B46" s="3">
         <v>0</v>
@@ -10757,18 +10825,12 @@
         <v>0</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
-      </c>
-      <c r="G46" s="3">
-        <v>0</v>
-      </c>
-      <c r="H46" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B47" s="3">
         <v>0</v>
@@ -10783,18 +10845,12 @@
         <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B48" s="3">
         <v>0</v>
@@ -10809,18 +10865,12 @@
         <v>0</v>
       </c>
       <c r="F48" s="3">
-        <v>0</v>
-      </c>
-      <c r="G48" s="3">
-        <v>0</v>
-      </c>
-      <c r="H48" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B49" s="3">
         <v>0</v>
@@ -10835,18 +10885,12 @@
         <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
-      </c>
-      <c r="G49" s="3">
-        <v>0</v>
-      </c>
-      <c r="H49" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="B50" s="3">
         <v>0</v>
@@ -10861,18 +10905,12 @@
         <v>0</v>
       </c>
       <c r="F50" s="3">
-        <v>0</v>
-      </c>
-      <c r="G50" s="3">
-        <v>0</v>
-      </c>
-      <c r="H50" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B51" s="3">
         <v>0</v>
@@ -10884,21 +10922,15 @@
         <v>0</v>
       </c>
       <c r="E51" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F51" s="3">
-        <v>0</v>
-      </c>
-      <c r="G51" s="3">
-        <v>1</v>
-      </c>
-      <c r="H51" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="B52" s="3">
         <v>0</v>
@@ -10913,18 +10945,12 @@
         <v>0</v>
       </c>
       <c r="F52" s="3">
-        <f>pow_Slime</f>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
-      <c r="H52" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B53" s="11">
         <v>0</v>
@@ -10939,18 +10965,12 @@
         <v>0</v>
       </c>
       <c r="F53" s="11">
-        <v>3</v>
-      </c>
-      <c r="G53" s="11">
-        <v>0</v>
-      </c>
-      <c r="H53" s="11">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="B54" s="3">
         <f>B$32*pw_Damage+B$33+B$34*pw_Poison+B$35*pw_Heal+B$36*pw_Shield+B$37*pw_Block+B$38*pw_Parry+B$39*pw_Dodge+B$40*pw_Strength*pw_Horizon+B$41*pw_Weaken*pw_Horizon+B$42*pw_Vulnerable*pw_Horizon+B$43*pw_Frozen+B$44*pw_Rooted+B$45*pw_Taunt+B$46*pw_Stealth+B$47*pw_PoisonBlade*pw_Horizon+B$48*pw_DoubleNextAttack+B$49*pw_DoubleShield+B$50*pw_Draw+B$51*pw_Move+B$52*pw_Summon+MAX(0,B$31-1)*pw_Area</f>
@@ -10967,16 +10987,10 @@
       <c r="F54" s="3">
         <f>F$32*pw_Damage+F$33+F$34*pw_Poison+F$35*pw_Heal+F$36*pw_Shield+F$37*pw_Block+F$38*pw_Parry+F$39*pw_Dodge+F$40*pw_Strength*pw_Horizon+F$41*pw_Weaken*pw_Horizon+F$42*pw_Vulnerable*pw_Horizon+F$43*pw_Frozen+F$44*pw_Rooted+F$45*pw_Taunt+F$46*pw_Stealth+F$47*pw_PoisonBlade*pw_Horizon+F$48*pw_DoubleNextAttack+F$49*pw_DoubleShield+F$50*pw_Draw+F$51*pw_Move+F$52*pw_Summon+MAX(0,F$31-1)*pw_Area</f>
       </c>
-      <c r="G54" s="3">
-        <f>G$32*pw_Damage+G$33+G$34*pw_Poison+G$35*pw_Heal+G$36*pw_Shield+G$37*pw_Block+G$38*pw_Parry+G$39*pw_Dodge+G$40*pw_Strength*pw_Horizon+G$41*pw_Weaken*pw_Horizon+G$42*pw_Vulnerable*pw_Horizon+G$43*pw_Frozen+G$44*pw_Rooted+G$45*pw_Taunt+G$46*pw_Stealth+G$47*pw_PoisonBlade*pw_Horizon+G$48*pw_DoubleNextAttack+G$49*pw_DoubleShield+G$50*pw_Draw+G$51*pw_Move+G$52*pw_Summon+MAX(0,G$31-1)*pw_Area</f>
-      </c>
-      <c r="H54" s="3">
-        <f>H$32*pw_Damage+H$33+H$34*pw_Poison+H$35*pw_Heal+H$36*pw_Shield+H$37*pw_Block+H$38*pw_Parry+H$39*pw_Dodge+H$40*pw_Strength*pw_Horizon+H$41*pw_Weaken*pw_Horizon+H$42*pw_Vulnerable*pw_Horizon+H$43*pw_Frozen+H$44*pw_Rooted+H$45*pw_Taunt+H$46*pw_Stealth+H$47*pw_PoisonBlade*pw_Horizon+H$48*pw_DoubleNextAttack+H$49*pw_DoubleShield+H$50*pw_Draw+H$51*pw_Move+H$52*pw_Summon+MAX(0,H$31-1)*pw_Area</f>
-      </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B55" s="3">
         <f>B$54-B$32*pw_Damage-B$33-B$52*pw_Summon</f>
@@ -10993,21 +11007,15 @@
       <c r="F55" s="3">
         <f>F$54-F$32*pw_Damage-F$33-F$52*pw_Summon</f>
       </c>
-      <c r="G55" s="3">
-        <f>G$54-G$32*pw_Damage-G$33-G$52*pw_Summon</f>
-      </c>
-      <c r="H55" s="3">
-        <f>H$54-H$32*pw_Damage-H$33-H$52*pw_Summon</f>
-      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="B57" s="4"/>
     </row>
   </sheetData>
-  <dataValidations count="11">
+  <dataValidations count="9">
     <dataValidation type="list" sqref="B10" showErrorMessage="0" allowBlank="1">
       <formula1>=list_Brain</formula1>
     </dataValidation>
@@ -11035,12 +11043,6 @@
     <dataValidation type="list" sqref="F24" showErrorMessage="0" allowBlank="1">
       <formula1>=list_EnemyCard</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G24" showErrorMessage="0" allowBlank="1">
-      <formula1>=list_EnemyCard</formula1>
-    </dataValidation>
-    <dataValidation type="list" sqref="H24" showErrorMessage="0" allowBlank="1">
-      <formula1>=list_EnemyCard</formula1>
-    </dataValidation>
   </dataValidations>
   <headerFooter/>
 </worksheet>
